--- a/キーエンス.xlsx
+++ b/キーエンス.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e484cef2ba5051b/ドキュメント/000-個人資料/00-brexa/20-PLC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1011701N\Documents\21-PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D066CA252ABDACC1048D53991F55A73EEDF55" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B653EF5-6184-49CF-8491-418A2F0CDE9F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E27A00-E929-428F-910D-EA0533E141AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="480" windowWidth="21600" windowHeight="11850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="VT ST KVのできること" sheetId="1" r:id="rId1"/>
+    <sheet name="インストール" sheetId="2" r:id="rId2"/>
+    <sheet name="ラダー" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,34 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
-  <si>
-    <r>
-      <t>以下に、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>キーエンス PLC のシミュレータ（VT ST：KV STUDIO のシミュレーション機能）で “できること／できないこと” をわかりやすく整理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>します。</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>※KV-3000／KV-7000／KV-8000 など、KV STUDIO 標準シミュレータ共通の内容です。</t>
   </si>
@@ -259,9 +235,6 @@
     <t>タイマー・内部メモリ</t>
   </si>
   <si>
-    <t>HMIとの連携</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">→ </t>
     </r>
@@ -308,14 +281,182 @@
     </r>
   </si>
   <si>
-    <t>必要なら…</t>
+    <t>キーエンス PLC のシミュレータ（VT ST：KV STUDIO のシミュレーション機能）で “できること／できないこと</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>直接キーボードでaを打つ</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>🛠 シミュレーション設定の手順</t>
+  </si>
+  <si>
+    <t>1. シミュレータモードを有効にする</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. メニューで </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>「モニタ／シミュレーション」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> を開く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 「シミュレータ」</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を選択します（ただ選ぶだけでまだ動作はしません） [niwakafa.com]</t>
+    </r>
+  </si>
+  <si>
+    <t>2. プログラムスキャンを開始する</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 次に </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>「デバッグ」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> メニューを開き、</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 「RU／連続スキャン実行」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> を選択します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">これでラダーが RUN 状態になり、シミュレーションが動作を開始します。 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[niwakafa.com]</t>
+    </r>
+  </si>
+  <si>
+    <t>下記のプロセスを行うこと。</t>
+    <rPh sb="0" eb="2">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>１.新規プロジェクト</t>
+    <rPh sb="2" eb="4">
+      <t>シンキ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>対応機種</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キシュ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>プロジェクト名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <rPh sb="0" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>PCの任意のフォルダー</t>
+    <rPh sb="3" eb="5">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>HMIとの連携</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +507,59 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="8"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,10 +578,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -401,8 +596,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -784,6 +999,1281 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>115397</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>181463</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F66C113E-C11A-AF4E-DA09-87357342F352}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="485775" y="257175"/>
+          <a:ext cx="7859222" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>100198</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>96302</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8E1B13C-010A-475B-A086-C935F0A77D1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="314325" y="4086225"/>
+          <a:ext cx="9387073" cy="6725702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>343563</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>162352</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62361160-92A3-F245-E28D-E25AF11091BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1076325" y="12106275"/>
+          <a:ext cx="4753638" cy="3057952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457838</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>219510</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3306F71-0569-B0CD-309B-5F363DD6D7C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="15678150"/>
+          <a:ext cx="4572638" cy="3115110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>505282</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66812</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAD9F82-DCFC-052D-0A88-0965D38CF88F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="514350"/>
+          <a:ext cx="3277057" cy="981212"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495864</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28909</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E69C2845-9295-108D-BAAE-267BCEB04294}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="2638425"/>
+          <a:ext cx="4039164" cy="2391109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>324412</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>162232</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811F05D7-31D6-1195-BF18-66E9EAB60E89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5210175" y="2724150"/>
+          <a:ext cx="4029637" cy="2200582"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>77152</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36B95392-0335-F72C-96E2-E40C4C3F37EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="800100" y="5600700"/>
+          <a:ext cx="6820852" cy="3581900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76909</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>143156</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F41CC417-4BDF-2187-B96B-8EC770EBD1F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1171575" y="9801225"/>
+          <a:ext cx="5077534" cy="2010056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="楕円 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{750E36BB-D96B-B14A-6FA1-AEF582DC0FB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5153025" y="8591550"/>
+          <a:ext cx="1143000" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="楕円 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1E245A2-F0A4-416D-B781-2DAC141B53CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2409825" y="11296650"/>
+          <a:ext cx="1143000" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>649193</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>10288</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45F09789-12F7-43FE-AA1B-07941B826FE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923925" y="12639675"/>
+          <a:ext cx="10698068" cy="5468113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="四角形: 角を丸くする 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0C255CE-637B-3113-512B-1E523FC0C646}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8896350" y="16611600"/>
+          <a:ext cx="2667000" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>667572</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>95671</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89548B17-0A74-A63A-ACD0-1F69F696ADAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952500" y="18507075"/>
+          <a:ext cx="5887272" cy="3019846"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>153027</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>171798</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA2EA2B-B760-3BC8-950E-6B78E641B76C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1143000" y="21964650"/>
+          <a:ext cx="4496427" cy="2495898"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="四角形: 角を丸くする 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F534AE8A-7810-4B10-AA28-68CAB4E904A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3190875" y="24050625"/>
+          <a:ext cx="2247900" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>124700</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>143044</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF5E715-6702-63A6-5C17-78B37874F736}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="714375" y="24888825"/>
+          <a:ext cx="6268325" cy="1209844"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="四角形: 角を丸くする 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B34D6E6-CA0E-4F12-BBEE-7922E0B9628C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5753100" y="25669875"/>
+          <a:ext cx="800100" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3C68E4D-C534-470E-97F1-00DA38A58F63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4419600" y="25679400"/>
+          <a:ext cx="800100" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>353451</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190794</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0090608C-FD7E-65FE-AD87-8E78385E8379}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="1181100"/>
+          <a:ext cx="7354326" cy="2105319"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57792</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>219433</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{428A0692-8C6B-AF4A-1BAF-7F2BEBA306F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="942975" y="3609975"/>
+          <a:ext cx="4601217" cy="2562583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>852</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>95501</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47455E1E-7B6D-C8CD-E528-8CE7759AD944}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8296275" y="8801100"/>
+          <a:ext cx="6106377" cy="1800476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矢印: 右 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9971AC4A-4863-5D55-EE1D-D9470F4787CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6419850" y="9286875"/>
+          <a:ext cx="1343025" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>228601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>681325</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A796D600-0F47-B1E5-0710-C6B8D97B3C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8258175" y="3800476"/>
+          <a:ext cx="2710150" cy="4876800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D19E0401-C29C-0544-4D40-8B98464F0231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6724650" y="6477000"/>
+          <a:ext cx="1409700" cy="1962150"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1052,63 +2542,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A188"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:A184"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:1" ht="33">
+      <c r="A1" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="39.75">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="38.5">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:1" ht="30">
+      <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="29">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="29">
+    <row r="9" spans="1:1" ht="30">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:1" ht="29">
+    <row r="10" spans="1:1" ht="30">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:1" ht="29">
+    <row r="11" spans="1:1" ht="30">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" ht="29">
+    <row r="12" spans="1:1" ht="30">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" ht="29">
+    <row r="13" spans="1:1" ht="30">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" ht="29">
+    <row r="14" spans="1:1" ht="30">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:1" ht="29">
+    <row r="15" spans="1:1" ht="30">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:1" ht="29">
+    <row r="16" spans="1:1" ht="30">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" ht="29">
+    <row r="17" spans="1:1" ht="30">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" ht="29">
+    <row r="18" spans="1:1" ht="30">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" ht="29">
+    <row r="19" spans="1:1" ht="30">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" ht="29">
+    <row r="20" spans="1:1" ht="30">
       <c r="A20" s="2"/>
     </row>
     <row r="24" spans="1:1">
@@ -1116,7 +2606,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -1124,7 +2614,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -1132,7 +2622,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -1140,12 +2630,12 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="30">
+      <c r="A35" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="29">
-      <c r="A35" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -1153,7 +2643,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -1161,7 +2651,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -1169,12 +2659,12 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="30">
+      <c r="A45" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="29">
-      <c r="A45" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -1182,7 +2672,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -1190,7 +2680,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -1198,12 +2688,12 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="30">
+      <c r="A55" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="29">
-      <c r="A55" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -1211,53 +2701,53 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="30">
+      <c r="A62" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="29">
-      <c r="A62" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="29">
+    <row r="63" spans="1:1" ht="30">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" spans="1:1" ht="29">
+    <row r="64" spans="1:1" ht="30">
       <c r="A64" s="2"/>
     </row>
-    <row r="65" spans="1:1" ht="29">
+    <row r="65" spans="1:1" ht="30">
       <c r="A65" s="2"/>
     </row>
-    <row r="66" spans="1:1" ht="29">
+    <row r="66" spans="1:1" ht="30">
       <c r="A66" s="2"/>
     </row>
-    <row r="67" spans="1:1" ht="29">
+    <row r="67" spans="1:1" ht="30">
       <c r="A67" s="2"/>
     </row>
-    <row r="68" spans="1:1" ht="29">
+    <row r="68" spans="1:1" ht="30">
       <c r="A68" s="2"/>
     </row>
-    <row r="69" spans="1:1" ht="29">
+    <row r="69" spans="1:1" ht="30">
       <c r="A69" s="2"/>
     </row>
-    <row r="70" spans="1:1" ht="29">
+    <row r="70" spans="1:1" ht="30">
       <c r="A70" s="2"/>
     </row>
-    <row r="71" spans="1:1" ht="29">
+    <row r="71" spans="1:1" ht="30">
       <c r="A71" s="2"/>
     </row>
-    <row r="72" spans="1:1" ht="29">
+    <row r="72" spans="1:1" ht="30">
       <c r="A72" s="2"/>
     </row>
-    <row r="73" spans="1:1" ht="29">
+    <row r="73" spans="1:1" ht="30">
       <c r="A73" s="2"/>
     </row>
-    <row r="74" spans="1:1" ht="29">
+    <row r="74" spans="1:1" ht="30">
       <c r="A74" s="2"/>
     </row>
     <row r="78" spans="1:1">
@@ -1265,7 +2755,7 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -1273,7 +2763,7 @@
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -1281,12 +2771,12 @@
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="30">
+      <c r="A87" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" ht="29">
-      <c r="A87" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -1294,7 +2784,7 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -1302,17 +2792,17 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="39.75">
+      <c r="A95" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="38.5">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:1" ht="30">
+      <c r="A97" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" ht="29">
-      <c r="A97" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -1320,7 +2810,7 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:1">
@@ -1328,7 +2818,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -1336,7 +2826,7 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -1344,17 +2834,17 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="30">
+      <c r="A110" s="2" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="29">
-      <c r="A110" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -1362,7 +2852,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -1370,7 +2860,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -1378,12 +2868,12 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="30">
+      <c r="A120" s="2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" ht="29">
-      <c r="A120" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:1">
@@ -1391,7 +2881,7 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:1">
@@ -1399,7 +2889,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -1407,12 +2897,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="30">
+      <c r="A130" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" ht="29">
-      <c r="A130" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -1420,7 +2910,7 @@
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136" spans="1:1">
@@ -1428,7 +2918,7 @@
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -1436,7 +2926,7 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -1444,17 +2934,17 @@
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="30">
+      <c r="A146" s="2" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" ht="29">
-      <c r="A146" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="147" spans="1:1">
@@ -1462,7 +2952,7 @@
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -1470,17 +2960,17 @@
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="30">
+      <c r="A155" s="2" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" ht="29">
-      <c r="A155" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="156" spans="1:1">
@@ -1488,7 +2978,7 @@
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="158" spans="1:1">
@@ -1496,7 +2986,7 @@
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160" spans="1:1">
@@ -1504,22 +2994,22 @@
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="39.75">
+      <c r="A166" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:1" ht="38.5">
-      <c r="A166" s="1" t="s">
+    <row r="168" spans="1:1" ht="22.5">
+      <c r="A168" s="4" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" ht="22">
-      <c r="A168" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="169" spans="1:1">
@@ -1527,7 +3017,7 @@
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171" spans="1:1">
@@ -1535,7 +3025,7 @@
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -1543,17 +3033,17 @@
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="3" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" ht="22">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="22.5">
       <c r="A177" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178" spans="1:1">
@@ -1561,7 +3051,7 @@
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -1569,7 +3059,7 @@
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="182" spans="1:1">
@@ -1577,17 +3067,69 @@
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" ht="38.5">
-      <c r="A188" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5131E-9A8A-4FBE-9443-8B2DC4394646}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F54D00-6BE9-4E9F-B164-020EF9E4E47B}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1595,4 +3137,88 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0746BD-CFEE-49F9-8213-217D3FE4109A}">
+  <dimension ref="B3:B42"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="21">
+      <c r="B31" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="6"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="6"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5"/>
+  <hyperlinks>
+    <hyperlink ref="B36" r:id="rId1" display="https://www.niwakafa.com/entry/2022/06/18/%E3%80%90%E5%88%9D%E7%B4%9A%E7%B7%A8%E3%80%91%E3%82%AD%E3%83%BC%E3%82%A8%E3%83%B3%E3%82%B9KV-8000_%E3%82%B7%E3%83%9F%E3%83%A5%E3%83%AC%E3%83%BC%E3%82%B7%E3%83%A7%E3%83%B3/%E3%82%B7%E3%83%9F%E3%83%A5%E3%83%AC" xr:uid="{CA96D331-B254-46EA-881A-9F92BB98BA4B}"/>
+    <hyperlink ref="B42" r:id="rId2" display="https://www.niwakafa.com/entry/2022/06/18/%E3%80%90%E5%88%9D%E7%B4%9A%E7%B7%A8%E3%80%91%E3%82%AD%E3%83%BC%E3%82%A8%E3%83%B3%E3%82%B9KV-8000_%E3%82%B7%E3%83%9F%E3%83%A5%E3%83%AC%E3%83%BC%E3%82%B7%E3%83%A7%E3%83%B3/%E3%82%B7%E3%83%9F%E3%83%A5%E3%83%AC" xr:uid="{B6505D02-0905-48C6-A886-E27814FF45E0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{21c43277-94c6-49b1-ae0c-d63b6a118fd5}" enabled="1" method="Privileged" siteId="{a54b00a2-87e8-4e92-a76d-de53269b7ddd}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>